--- a/tracker/2250823/Open_Questions.xlsx
+++ b/tracker/2250823/Open_Questions.xlsx
@@ -441,7 +441,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C12"/>
+  <dimension ref="A1:C13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -459,7 +459,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>6 open - ready to ship when this is 0 and every unit and filter is accounted for</t>
+          <t>4 open - ready to ship when this is 0 and every unit and filter is accounted for</t>
         </is>
       </c>
     </row>
@@ -488,7 +488,7 @@
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>Which RTUs got which size? 4 RTUs (1A,2A,1C,2C) need 48 of 2", only 36 ordered; 12 extra 4" ordered. Did any of those four get filters yet, and what size?</t>
+          <t>Possible size substitution on set 2: 4" filters may have been installed in some 2" RTUs (1A, 2A, 1C, 2C). 48 of 2" needed, 36 ordered; 12 extra 4" ordered. Which units got which? (Angel's theory, unconfirmed)</t>
         </is>
       </c>
       <c r="C4" s="4" t="inlineStr">
@@ -505,7 +505,7 @@
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>Are the 12 extra 4" filters (8 of 20x25x4, 4 of 20x20x4) RTU-2B-2's? When will 2B-2 be done?</t>
+          <t>Are the 12 extra 4" filters (8 of 20x25x4, 4 of 20x20x4) RTU-2B-2's, or were they used as substitutes? When will 2B-2 be done?</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
@@ -539,7 +539,7 @@
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>AHU-1 and ERV-1: are the sizes right (20x24 vs the RTUs' 20x25) and are they still not replaced?</t>
+          <t>AHU-1 and ERV-1 are not replaced yet. Are their sizes right (20x24 vs the RTUs' 20x25)? Set 3 must match the spec size exactly.</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr">
@@ -549,14 +549,14 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="3" t="inlineStr">
-        <is>
-          <t>Open</t>
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>Answered</t>
         </is>
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>Project phase for this job (blank for now).</t>
+          <t>Phase: none right now. Added scope may come as a phase on this job number or a new job number; jobs are always separated by job number.</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr">
@@ -566,19 +566,19 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="3" t="inlineStr">
-        <is>
-          <t>Open</t>
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>Answered</t>
         </is>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>Sets 3 (final, MERV 13) and attic stock: any quantity or timing planned?</t>
+          <t>Attic stock: none planned. The PM can add it at any time (MERV 13).</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>Jordan (PM)</t>
+          <t>Angel</t>
         </is>
       </c>
     </row>
@@ -590,7 +590,7 @@
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>PO numbers: 380118 for the 12-filter order, 382244 for the 60-filter order.</t>
+          <t>AHU-1 and ERV-1 not replaced yet.</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr">
@@ -607,7 +607,7 @@
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>Order 1 date is 9/22/2026 (not 9/25).</t>
+          <t>PO numbers: 380118 for the 12-filter order, 382244 for the 60-filter order.</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
@@ -624,10 +624,27 @@
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
+          <t>Order 1 date is 9/22/2026 (not 9/25).</t>
+        </is>
+      </c>
+      <c r="C12" s="4" t="inlineStr">
+        <is>
+          <t>Angel</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>Answered</t>
+        </is>
+      </c>
+      <c r="B13" s="4" t="inlineStr">
+        <is>
           <t>Both orders are Set 2, MERV 8.</t>
         </is>
       </c>
-      <c r="C12" s="4" t="inlineStr">
+      <c r="C13" s="4" t="inlineStr">
         <is>
           <t>Angel</t>
         </is>

--- a/tracker/2250823/Open_Questions.xlsx
+++ b/tracker/2250823/Open_Questions.xlsx
@@ -441,7 +441,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C13"/>
+  <dimension ref="A1:C14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -488,7 +488,7 @@
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>Possible size substitution on set 2: 4" filters may have been installed in some 2" RTUs (1A, 2A, 1C, 2C). 48 of 2" needed, 36 ordered; 12 extra 4" ordered. Which units got which? (Angel's theory, unconfirmed)</t>
+          <t>All 7 RTUs need 84 filters, only 72 ordered: one RTU's worth (12) short overall. Either 1 of the 2" RTUs (1A, 2A, 1C, 2C) still needs 2" (8 of 20x25x2 + 4 of 20x20x2), or a 2" unit got 4" and RTU-2B-1 will be short on 4". Which units got what size?</t>
         </is>
       </c>
       <c r="C4" s="4" t="inlineStr">
@@ -505,12 +505,12 @@
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>Are the 12 extra 4" filters (8 of 20x25x4, 4 of 20x20x4) RTU-2B-2's, or were they used as substitutes? When will 2B-2 be done?</t>
+          <t>For each order, which units did the filters go to (fills the 'Units it went to' column)?</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>Angel</t>
+          <t>Techs</t>
         </is>
       </c>
     </row>
@@ -522,12 +522,12 @@
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>For each order, which units did the filters go to (fills the 'Units it went to' column)?</t>
+          <t>When will RTU-2B-1 be started? The extra 12 4" filters ordered are on hand for it unless they were used as substitutes.</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>Techs</t>
+          <t>Angel</t>
         </is>
       </c>
     </row>
@@ -556,7 +556,7 @@
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>Phase: none right now. Added scope may come as a phase on this job number or a new job number; jobs are always separated by job number.</t>
+          <t>RTU-2B-1 (not 2B-2) is the one RTU not started up yet. 6 of 7 RTUs replaced.</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr">
@@ -573,7 +573,7 @@
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>Attic stock: none planned. The PM can add it at any time (MERV 13).</t>
+          <t>Phase: none right now. Added scope may come as a phase on this job number or a new job number; jobs are always separated by job number.</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr">
@@ -590,7 +590,7 @@
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>AHU-1 and ERV-1 not replaced yet.</t>
+          <t>Attic stock: none planned. The PM can add it at any time (MERV 13).</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr">
@@ -607,7 +607,7 @@
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>PO numbers: 380118 for the 12-filter order, 382244 for the 60-filter order.</t>
+          <t>AHU-1 and ERV-1 not replaced yet.</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
@@ -624,7 +624,7 @@
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>Order 1 date is 9/22/2026 (not 9/25).</t>
+          <t>PO numbers: 380118 for the 12-filter order, 382244 for the 60-filter order.</t>
         </is>
       </c>
       <c r="C12" s="4" t="inlineStr">
@@ -641,10 +641,27 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
+          <t>Order 1 date is 9/22/2026 (not 9/25).</t>
+        </is>
+      </c>
+      <c r="C13" s="4" t="inlineStr">
+        <is>
+          <t>Angel</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>Answered</t>
+        </is>
+      </c>
+      <c r="B14" s="4" t="inlineStr">
+        <is>
           <t>Both orders are Set 2, MERV 8.</t>
         </is>
       </c>
-      <c r="C13" s="4" t="inlineStr">
+      <c r="C14" s="4" t="inlineStr">
         <is>
           <t>Angel</t>
         </is>
